--- a/public/results/2025/2025 Weekly Stats - Week 12.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0AE596-D64F-B042-90AC-4B25AC345106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD239960-DFDC-1344-A761-9FE852991918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45600" yWindow="1640" windowWidth="26740" windowHeight="18000" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44200" yWindow="2000" windowWidth="26740" windowHeight="18000" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="14" r:id="rId1"/>
@@ -26,10 +26,11 @@
     <sheet name="Week 9" sheetId="27" r:id="rId11"/>
     <sheet name="Week 10" sheetId="28" r:id="rId12"/>
     <sheet name="Week 11" sheetId="29" r:id="rId13"/>
+    <sheet name="Week 12" sheetId="30" r:id="rId14"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId14"/>
     <externalReference r:id="rId15"/>
+    <externalReference r:id="rId16"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="39">
   <si>
     <t>Points</t>
   </si>
@@ -415,7 +416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -579,6 +580,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -595,7 +599,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1188,23 +1201,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -1218,23 +1231,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -2080,23 +2093,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -2110,23 +2123,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -3648,23 +3661,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -3678,23 +3691,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -4979,23 +4992,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -5009,23 +5022,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -6430,23 +6443,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -6460,23 +6473,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -6824,7 +6837,7 @@
       <c r="J9" s="12">
         <v>6</v>
       </c>
-      <c r="K9" s="67">
+      <c r="K9" s="61">
         <v>4</v>
       </c>
       <c r="L9" s="13">
@@ -7160,13 +7173,13 @@
       <c r="E15" s="12">
         <v>4</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="61">
         <v>2</v>
       </c>
       <c r="G15" s="12">
         <v>5</v>
       </c>
-      <c r="H15" s="67">
+      <c r="H15" s="61">
         <v>3</v>
       </c>
       <c r="I15" s="12">
@@ -7277,7 +7290,7 @@
       <c r="E17" s="12">
         <v>4</v>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="61">
         <v>2</v>
       </c>
       <c r="G17" s="12">
@@ -7973,7 +7986,7 @@
       <c r="C29" s="12">
         <v>6</v>
       </c>
-      <c r="D29" s="67">
+      <c r="D29" s="61">
         <v>4</v>
       </c>
       <c r="E29" s="12">
@@ -8211,6 +8224,1808 @@
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
     <ignoredError sqref="L12 L16" formula="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1BBB3E6-C6EE-6A4F-8D6A-361AF94230C4}">
+  <dimension ref="A1:Z32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" style="2" customWidth="1"/>
+    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+    </row>
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+    </row>
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+    </row>
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="20">
+        <v>1</v>
+      </c>
+      <c r="D4" s="20">
+        <v>2</v>
+      </c>
+      <c r="E4" s="20">
+        <v>3</v>
+      </c>
+      <c r="F4" s="20">
+        <v>4</v>
+      </c>
+      <c r="G4" s="20">
+        <v>5</v>
+      </c>
+      <c r="H4" s="20">
+        <v>6</v>
+      </c>
+      <c r="I4" s="20">
+        <v>7</v>
+      </c>
+      <c r="J4" s="20">
+        <v>8</v>
+      </c>
+      <c r="K4" s="20">
+        <v>9</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+    </row>
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A5" s="22"/>
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6">
+        <v>5</v>
+      </c>
+      <c r="E5" s="6">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6">
+        <v>4</v>
+      </c>
+      <c r="H5" s="6">
+        <v>4</v>
+      </c>
+      <c r="I5" s="6">
+        <v>3</v>
+      </c>
+      <c r="J5" s="6">
+        <v>4</v>
+      </c>
+      <c r="K5" s="6">
+        <v>5</v>
+      </c>
+      <c r="L5" s="7">
+        <f>SUM(C5:K5)</f>
+        <v>36</v>
+      </c>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+    </row>
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+      <c r="B6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="25">
+        <v>4</v>
+      </c>
+      <c r="D6" s="25">
+        <v>1</v>
+      </c>
+      <c r="E6" s="25">
+        <v>3</v>
+      </c>
+      <c r="F6" s="25">
+        <v>9</v>
+      </c>
+      <c r="G6" s="25">
+        <v>5</v>
+      </c>
+      <c r="H6" s="25">
+        <v>7</v>
+      </c>
+      <c r="I6" s="25">
+        <v>8</v>
+      </c>
+      <c r="J6" s="25">
+        <v>6</v>
+      </c>
+      <c r="K6" s="25">
+        <v>2</v>
+      </c>
+      <c r="L6" s="26"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+    </row>
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="12">
+        <v>5</v>
+      </c>
+      <c r="D7" s="12">
+        <v>8</v>
+      </c>
+      <c r="E7" s="12">
+        <v>5</v>
+      </c>
+      <c r="F7" s="12">
+        <v>4</v>
+      </c>
+      <c r="G7" s="12">
+        <v>8</v>
+      </c>
+      <c r="H7" s="12">
+        <v>6</v>
+      </c>
+      <c r="I7" s="12">
+        <v>6</v>
+      </c>
+      <c r="J7" s="12">
+        <v>6</v>
+      </c>
+      <c r="K7" s="12">
+        <v>8</v>
+      </c>
+      <c r="L7" s="13">
+        <f t="shared" ref="L7:L32" si="0">IF(SUM(C7:K7)&gt;0, SUM(C7:K7),"")</f>
+        <v>56</v>
+      </c>
+      <c r="M7" s="12">
+        <v>18</v>
+      </c>
+      <c r="N7" s="12">
+        <f>IF(L7&lt;&gt;"",L7- M7, "")</f>
+        <v>38</v>
+      </c>
+      <c r="O7" s="14"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+    </row>
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="16">
+        <f>IF(C7&gt;0, VLOOKUP(C7-C$5-(INT($M7/9)+(MOD($M7,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="D8" s="16">
+        <f>IF(D7&gt;0, VLOOKUP(D7-D$5-(INT($M7/9)+(MOD($M7,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="16">
+        <f>IF(E7&gt;0, VLOOKUP(E7-E$5-(INT($M7/9)+(MOD($M7,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="F8" s="16">
+        <f>IF(F7&gt;0, VLOOKUP(F7-F$5-(INT($M7/9)+(MOD($M7,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="G8" s="16">
+        <f>IF(G7&gt;0, VLOOKUP(G7-G$5-(INT($M7/9)+(MOD($M7,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <f>IF(H7&gt;0, VLOOKUP(H7-H$5-(INT($M7/9)+(MOD($M7,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="I8" s="16">
+        <f>IF(I7&gt;0, VLOOKUP(I7-I$5-(INT($M7/9)+(MOD($M7,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="J8" s="16">
+        <f>IF(J7&gt;0, VLOOKUP(J7-J$5-(INT($M7/9)+(MOD($M7,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="K8" s="16">
+        <f>IF(K7&gt;0, VLOOKUP(K7-K$5-(INT($M7/9)+(MOD($M7,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="L8" s="17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="18">
+        <f>IF(L8&lt;&gt;"", L8, "")</f>
+        <v>16</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+    </row>
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="68">
+        <v>6</v>
+      </c>
+      <c r="D9" s="68">
+        <v>5</v>
+      </c>
+      <c r="E9" s="68">
+        <v>5</v>
+      </c>
+      <c r="F9" s="68">
+        <v>4</v>
+      </c>
+      <c r="G9" s="68">
+        <v>6</v>
+      </c>
+      <c r="H9" s="68">
+        <v>4</v>
+      </c>
+      <c r="I9" s="68">
+        <v>3</v>
+      </c>
+      <c r="J9" s="68">
+        <v>5</v>
+      </c>
+      <c r="K9" s="68">
+        <v>6</v>
+      </c>
+      <c r="L9" s="69">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="M9" s="12">
+        <v>7</v>
+      </c>
+      <c r="N9" s="12">
+        <f>IF(L9&lt;&gt;"",L9- M9, "")</f>
+        <v>37</v>
+      </c>
+      <c r="O9" s="14"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+    </row>
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="70">
+        <f>IF(C9&gt;0, VLOOKUP(C9-C$5-(INT($M9/9)+(MOD($M9,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="D10" s="70">
+        <f>IF(D9&gt;0, VLOOKUP(D9-D$5-(INT($M9/9)+(MOD($M9,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="E10" s="70">
+        <f>IF(E9&gt;0, VLOOKUP(E9-E$5-(INT($M9/9)+(MOD($M9,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="70">
+        <f>IF(F9&gt;0, VLOOKUP(F9-F$5-(INT($M9/9)+(MOD($M9,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="70">
+        <f>IF(G9&gt;0, VLOOKUP(G9-G$5-(INT($M9/9)+(MOD($M9,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="70">
+        <f>IF(H9&gt;0, VLOOKUP(H9-H$5-(INT($M9/9)+(MOD($M9,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="I10" s="70">
+        <f>IF(I9&gt;0, VLOOKUP(I9-I$5-(INT($M9/9)+(MOD($M9,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="J10" s="70">
+        <f>IF(J9&gt;0, VLOOKUP(J9-J$5-(INT($M9/9)+(MOD($M9,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="K10" s="70">
+        <f>IF(K9&gt;0, VLOOKUP(K9-K$5-(INT($M9/9)+(MOD($M9,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="L10" s="71">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="18">
+        <f>IF(L10&lt;&gt;"", L10, "")</f>
+        <v>17</v>
+      </c>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+    </row>
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="68">
+        <v>5</v>
+      </c>
+      <c r="D11" s="68">
+        <v>7</v>
+      </c>
+      <c r="E11" s="68">
+        <v>5</v>
+      </c>
+      <c r="F11" s="68">
+        <v>4</v>
+      </c>
+      <c r="G11" s="68">
+        <v>6</v>
+      </c>
+      <c r="H11" s="68">
+        <v>5</v>
+      </c>
+      <c r="I11" s="68">
+        <v>3</v>
+      </c>
+      <c r="J11" s="68">
+        <v>5</v>
+      </c>
+      <c r="K11" s="68">
+        <v>7</v>
+      </c>
+      <c r="L11" s="69">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="M11" s="12">
+        <v>9</v>
+      </c>
+      <c r="N11" s="12">
+        <f>IF(L11&lt;&gt;"",L11- M11, "")</f>
+        <v>38</v>
+      </c>
+      <c r="O11" s="14"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+    </row>
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="70">
+        <f>IF(C11&gt;0, VLOOKUP(C11-C$5-(INT($M11/9)+(MOD($M11,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="D12" s="70">
+        <f>IF(D11&gt;0, VLOOKUP(D11-D$5-(INT($M11/9)+(MOD($M11,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="70">
+        <f>IF(E11&gt;0, VLOOKUP(E11-E$5-(INT($M11/9)+(MOD($M11,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="F12" s="70">
+        <f>IF(F11&gt;0, VLOOKUP(F11-F$5-(INT($M11/9)+(MOD($M11,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G12" s="70">
+        <f>IF(G11&gt;0, VLOOKUP(G11-G$5-(INT($M11/9)+(MOD($M11,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="70">
+        <f>IF(H11&gt;0, VLOOKUP(H11-H$5-(INT($M11/9)+(MOD($M11,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="I12" s="70">
+        <f>IF(I11&gt;0, VLOOKUP(I11-I$5-(INT($M11/9)+(MOD($M11,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="J12" s="70">
+        <f>IF(J11&gt;0, VLOOKUP(J11-J$5-(INT($M11/9)+(MOD($M11,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="K12" s="70">
+        <f>IF(K11&gt;0, VLOOKUP(K11-K$5-(INT($M11/9)+(MOD($M11,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="L12" s="71">
+        <f t="shared" ref="L12" si="1">IF(SUM(C12:K12)&gt;0, SUM(C12:K12),"")</f>
+        <v>16</v>
+      </c>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="18">
+        <f>IF(L12&lt;&gt;"", L12, "")</f>
+        <v>16</v>
+      </c>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+    </row>
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="68">
+        <v>5</v>
+      </c>
+      <c r="D13" s="68">
+        <v>7</v>
+      </c>
+      <c r="E13" s="68">
+        <v>5</v>
+      </c>
+      <c r="F13" s="68">
+        <v>5</v>
+      </c>
+      <c r="G13" s="68">
+        <v>6</v>
+      </c>
+      <c r="H13" s="68">
+        <v>5</v>
+      </c>
+      <c r="I13" s="68">
+        <v>4</v>
+      </c>
+      <c r="J13" s="68">
+        <v>6</v>
+      </c>
+      <c r="K13" s="68">
+        <v>7</v>
+      </c>
+      <c r="L13" s="69">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="M13" s="12">
+        <v>11</v>
+      </c>
+      <c r="N13" s="12">
+        <f>IF(L13&lt;&gt;"",L13- M13, "")</f>
+        <v>39</v>
+      </c>
+      <c r="O13" s="14"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+    </row>
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="70">
+        <f>IF(C13&gt;0, VLOOKUP(C13-C$5-(INT($M13/9)+(MOD($M13,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="D14" s="70">
+        <f>IF(D13&gt;0, VLOOKUP(D13-D$5-(INT($M13/9)+(MOD($M13,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="E14" s="70">
+        <f>IF(E13&gt;0, VLOOKUP(E13-E$5-(INT($M13/9)+(MOD($M13,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="F14" s="70">
+        <f>IF(F13&gt;0, VLOOKUP(F13-F$5-(INT($M13/9)+(MOD($M13,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="70">
+        <f>IF(G13&gt;0, VLOOKUP(G13-G$5-(INT($M13/9)+(MOD($M13,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="70">
+        <f>IF(H13&gt;0, VLOOKUP(H13-H$5-(INT($M13/9)+(MOD($M13,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="I14" s="70">
+        <f>IF(I13&gt;0, VLOOKUP(I13-I$5-(INT($M13/9)+(MOD($M13,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="J14" s="70">
+        <f>IF(J13&gt;0, VLOOKUP(J13-J$5-(INT($M13/9)+(MOD($M13,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="70">
+        <f>IF(K13&gt;0, VLOOKUP(K13-K$5-(INT($M13/9)+(MOD($M13,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="L14" s="71">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="18">
+        <f>IF(L14&lt;&gt;"", L14, "")</f>
+        <v>15</v>
+      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+    </row>
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="68">
+        <v>5</v>
+      </c>
+      <c r="D15" s="68">
+        <v>7</v>
+      </c>
+      <c r="E15" s="68">
+        <v>5</v>
+      </c>
+      <c r="F15" s="68">
+        <v>5</v>
+      </c>
+      <c r="G15" s="68">
+        <v>6</v>
+      </c>
+      <c r="H15" s="68">
+        <v>7</v>
+      </c>
+      <c r="I15" s="68">
+        <v>5</v>
+      </c>
+      <c r="J15" s="68">
+        <v>5</v>
+      </c>
+      <c r="K15" s="68">
+        <v>7</v>
+      </c>
+      <c r="L15" s="69">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="M15" s="12">
+        <v>11</v>
+      </c>
+      <c r="N15" s="12">
+        <f>IF(L15&lt;&gt;"",L15- M15, "")</f>
+        <v>41</v>
+      </c>
+      <c r="O15" s="14"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+    </row>
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="70">
+        <f>IF(C15&gt;0, VLOOKUP(C15-C$5-(INT($M15/9)+(MOD($M15,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="D16" s="70">
+        <f>IF(D15&gt;0, VLOOKUP(D15-D$5-(INT($M15/9)+(MOD($M15,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="E16" s="70">
+        <f>IF(E15&gt;0, VLOOKUP(E15-E$5-(INT($M15/9)+(MOD($M15,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="F16" s="70">
+        <f>IF(F15&gt;0, VLOOKUP(F15-F$5-(INT($M15/9)+(MOD($M15,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="G16" s="70">
+        <f>IF(G15&gt;0, VLOOKUP(G15-G$5-(INT($M15/9)+(MOD($M15,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="H16" s="70">
+        <f>IF(H15&gt;0, VLOOKUP(H15-H$5-(INT($M15/9)+(MOD($M15,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="70">
+        <f>IF(I15&gt;0, VLOOKUP(I15-I$5-(INT($M15/9)+(MOD($M15,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="70">
+        <f>IF(J15&gt;0, VLOOKUP(J15-J$5-(INT($M15/9)+(MOD($M15,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="K16" s="70">
+        <f>IF(K15&gt;0, VLOOKUP(K15-K$5-(INT($M15/9)+(MOD($M15,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="L16" s="71">
+        <f t="shared" ref="L16" si="2">IF(SUM(C16:K16)&gt;0, SUM(C16:K16),"")</f>
+        <v>13</v>
+      </c>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="18">
+        <f>IF(L16&lt;&gt;"", L16, "")</f>
+        <v>13</v>
+      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+    </row>
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="68">
+        <v>5</v>
+      </c>
+      <c r="D17" s="68">
+        <v>6</v>
+      </c>
+      <c r="E17" s="68">
+        <v>5</v>
+      </c>
+      <c r="F17" s="68">
+        <v>6</v>
+      </c>
+      <c r="G17" s="68">
+        <v>8</v>
+      </c>
+      <c r="H17" s="68">
+        <v>5</v>
+      </c>
+      <c r="I17" s="68">
+        <v>6</v>
+      </c>
+      <c r="J17" s="68">
+        <v>6</v>
+      </c>
+      <c r="K17" s="68">
+        <v>7</v>
+      </c>
+      <c r="L17" s="69">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="M17" s="12">
+        <v>18</v>
+      </c>
+      <c r="N17" s="12">
+        <f>IF(L17&lt;&gt;"",L17- M17, "")</f>
+        <v>36</v>
+      </c>
+      <c r="O17" s="14"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+    </row>
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="70">
+        <f>IF(C17&gt;0, VLOOKUP(C17-C$5-(INT($M17/9)+(MOD($M17,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="D18" s="70">
+        <f>IF(D17&gt;0, VLOOKUP(D17-D$5-(INT($M17/9)+(MOD($M17,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="E18" s="70">
+        <f>IF(E17&gt;0, VLOOKUP(E17-E$5-(INT($M17/9)+(MOD($M17,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="F18" s="70">
+        <f>IF(F17&gt;0, VLOOKUP(F17-F$5-(INT($M17/9)+(MOD($M17,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="G18" s="70">
+        <f>IF(G17&gt;0, VLOOKUP(G17-G$5-(INT($M17/9)+(MOD($M17,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="70">
+        <f>IF(H17&gt;0, VLOOKUP(H17-H$5-(INT($M17/9)+(MOD($M17,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="I18" s="70">
+        <f>IF(I17&gt;0, VLOOKUP(I17-I$5-(INT($M17/9)+(MOD($M17,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="J18" s="70">
+        <f>IF(J17&gt;0, VLOOKUP(J17-J$5-(INT($M17/9)+(MOD($M17,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="K18" s="70">
+        <f>IF(K17&gt;0, VLOOKUP(K17-K$5-(INT($M17/9)+(MOD($M17,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="L18" s="71">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="18">
+        <f>IF(L18&lt;&gt;"", L18, "")</f>
+        <v>18</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+    </row>
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="68">
+        <v>8</v>
+      </c>
+      <c r="D19" s="68">
+        <v>5</v>
+      </c>
+      <c r="E19" s="68">
+        <v>5</v>
+      </c>
+      <c r="F19" s="68">
+        <v>3</v>
+      </c>
+      <c r="G19" s="68">
+        <v>6</v>
+      </c>
+      <c r="H19" s="68">
+        <v>5</v>
+      </c>
+      <c r="I19" s="68">
+        <v>6</v>
+      </c>
+      <c r="J19" s="68">
+        <v>6</v>
+      </c>
+      <c r="K19" s="68">
+        <v>6</v>
+      </c>
+      <c r="L19" s="69">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="M19" s="12">
+        <v>14</v>
+      </c>
+      <c r="N19" s="12">
+        <f>IF(L19&lt;&gt;"",L19- M19, "")</f>
+        <v>36</v>
+      </c>
+      <c r="O19" s="14"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+    </row>
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="70">
+        <f>IF(C19&gt;0, VLOOKUP(C19-C$5-(INT($M19/9)+(MOD($M19,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="70">
+        <f>IF(D19&gt;0, VLOOKUP(D19-D$5-(INT($M19/9)+(MOD($M19,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>4</v>
+      </c>
+      <c r="E20" s="70">
+        <f>IF(E19&gt;0, VLOOKUP(E19-E$5-(INT($M19/9)+(MOD($M19,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="F20" s="70">
+        <f>IF(F19&gt;0, VLOOKUP(F19-F$5-(INT($M19/9)+(MOD($M19,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="G20" s="70">
+        <f>IF(G19&gt;0, VLOOKUP(G19-G$5-(INT($M19/9)+(MOD($M19,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="H20" s="70">
+        <f>IF(H19&gt;0, VLOOKUP(H19-H$5-(INT($M19/9)+(MOD($M19,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="I20" s="70">
+        <f>IF(I19&gt;0, VLOOKUP(I19-I$5-(INT($M19/9)+(MOD($M19,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="70">
+        <f>IF(J19&gt;0, VLOOKUP(J19-J$5-(INT($M19/9)+(MOD($M19,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="K20" s="70">
+        <f>IF(K19&gt;0, VLOOKUP(K19-K$5-(INT($M19/9)+(MOD($M19,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="L20" s="71">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="18">
+        <f>IF(L20&lt;&gt;"", L20, "")</f>
+        <v>18</v>
+      </c>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+    </row>
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="68">
+        <v>4</v>
+      </c>
+      <c r="D21" s="68">
+        <v>5</v>
+      </c>
+      <c r="E21" s="68">
+        <v>4</v>
+      </c>
+      <c r="F21" s="68">
+        <v>4</v>
+      </c>
+      <c r="G21" s="68">
+        <v>4</v>
+      </c>
+      <c r="H21" s="68">
+        <v>4</v>
+      </c>
+      <c r="I21" s="68">
+        <v>3</v>
+      </c>
+      <c r="J21" s="68">
+        <v>5</v>
+      </c>
+      <c r="K21" s="68">
+        <v>5</v>
+      </c>
+      <c r="L21" s="69">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="M21" s="12">
+        <v>2</v>
+      </c>
+      <c r="N21" s="12">
+        <f>IF(L21&lt;&gt;"",L21- M21, "")</f>
+        <v>36</v>
+      </c>
+      <c r="O21" s="14"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+    </row>
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="70">
+        <f>IF(C21&gt;0, VLOOKUP(C21-C$5-(INT($M21/9)+(MOD($M21,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="D22" s="70">
+        <f>IF(D21&gt;0, VLOOKUP(D21-D$5-(INT($M21/9)+(MOD($M21,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="E22" s="70">
+        <f>IF(E21&gt;0, VLOOKUP(E21-E$5-(INT($M21/9)+(MOD($M21,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="F22" s="70">
+        <f>IF(F21&gt;0, VLOOKUP(F21-F$5-(INT($M21/9)+(MOD($M21,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="G22" s="70">
+        <f>IF(G21&gt;0, VLOOKUP(G21-G$5-(INT($M21/9)+(MOD($M21,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="H22" s="70">
+        <f>IF(H21&gt;0, VLOOKUP(H21-H$5-(INT($M21/9)+(MOD($M21,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="I22" s="70">
+        <f>IF(I21&gt;0, VLOOKUP(I21-I$5-(INT($M21/9)+(MOD($M21,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="J22" s="70">
+        <f>IF(J21&gt;0, VLOOKUP(J21-J$5-(INT($M21/9)+(MOD($M21,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="K22" s="70">
+        <f>IF(K21&gt;0, VLOOKUP(K21-K$5-(INT($M21/9)+(MOD($M21,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="L22" s="71">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="18">
+        <f>IF(L22&lt;&gt;"", L22, "")</f>
+        <v>18</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+    </row>
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="68">
+        <v>5</v>
+      </c>
+      <c r="D23" s="68">
+        <v>5</v>
+      </c>
+      <c r="E23" s="68">
+        <v>5</v>
+      </c>
+      <c r="F23" s="68">
+        <v>4</v>
+      </c>
+      <c r="G23" s="68">
+        <v>4</v>
+      </c>
+      <c r="H23" s="68">
+        <v>4</v>
+      </c>
+      <c r="I23" s="68">
+        <v>4</v>
+      </c>
+      <c r="J23" s="68">
+        <v>4</v>
+      </c>
+      <c r="K23" s="68">
+        <v>6</v>
+      </c>
+      <c r="L23" s="69">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="M23" s="12">
+        <v>9</v>
+      </c>
+      <c r="N23" s="12">
+        <f>IF(L23&lt;&gt;"",L23- M23, "")</f>
+        <v>32</v>
+      </c>
+      <c r="O23" s="14"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+    </row>
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="70">
+        <f>IF(C23&gt;0, VLOOKUP(C23-C$5-(INT($M23/9)+(MOD($M23,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="D24" s="70">
+        <f>IF(D23&gt;0, VLOOKUP(D23-D$5-(INT($M23/9)+(MOD($M23,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="E24" s="70">
+        <f>IF(E23&gt;0, VLOOKUP(E23-E$5-(INT($M23/9)+(MOD($M23,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="F24" s="70">
+        <f>IF(F23&gt;0, VLOOKUP(F23-F$5-(INT($M23/9)+(MOD($M23,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G24" s="70">
+        <f>IF(G23&gt;0, VLOOKUP(G23-G$5-(INT($M23/9)+(MOD($M23,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="H24" s="70">
+        <f>IF(H23&gt;0, VLOOKUP(H23-H$5-(INT($M23/9)+(MOD($M23,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="I24" s="70">
+        <f>IF(I23&gt;0, VLOOKUP(I23-I$5-(INT($M23/9)+(MOD($M23,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="J24" s="70">
+        <f>IF(J23&gt;0, VLOOKUP(J23-J$5-(INT($M23/9)+(MOD($M23,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="K24" s="70">
+        <f>IF(K23&gt;0, VLOOKUP(K23-K$5-(INT($M23/9)+(MOD($M23,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="L24" s="71">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="18">
+        <f>IF(L24&lt;&gt;"", L24, "")</f>
+        <v>22</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+    </row>
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="68">
+        <v>6</v>
+      </c>
+      <c r="D25" s="68">
+        <v>10</v>
+      </c>
+      <c r="E25" s="68">
+        <v>8</v>
+      </c>
+      <c r="F25" s="68">
+        <v>6</v>
+      </c>
+      <c r="G25" s="68">
+        <v>8</v>
+      </c>
+      <c r="H25" s="68">
+        <v>8</v>
+      </c>
+      <c r="I25" s="68">
+        <v>6</v>
+      </c>
+      <c r="J25" s="68">
+        <v>8</v>
+      </c>
+      <c r="K25" s="68">
+        <v>10</v>
+      </c>
+      <c r="L25" s="69">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="M25" s="12">
+        <v>22</v>
+      </c>
+      <c r="N25" s="12">
+        <f>IF(L25&lt;&gt;"",L25- M25, "")</f>
+        <v>48</v>
+      </c>
+      <c r="O25" s="14"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+    </row>
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="15"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="70">
+        <f>IF(C25&gt;0, VLOOKUP(C25-C$5-(INT($M25/9)+(MOD($M25,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="D26" s="70">
+        <f>IF(D25&gt;0, VLOOKUP(D25-D$5-(INT($M25/9)+(MOD($M25,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="70">
+        <f>IF(E25&gt;0, VLOOKUP(E25-E$5-(INT($M25/9)+(MOD($M25,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="F26" s="70">
+        <f>IF(F25&gt;0, VLOOKUP(F25-F$5-(INT($M25/9)+(MOD($M25,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="G26" s="70">
+        <f>IF(G25&gt;0, VLOOKUP(G25-G$5-(INT($M25/9)+(MOD($M25,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="70">
+        <f>IF(H25&gt;0, VLOOKUP(H25-H$5-(INT($M25/9)+(MOD($M25,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="70">
+        <f>IF(I25&gt;0, VLOOKUP(I25-I$5-(INT($M25/9)+(MOD($M25,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="J26" s="70">
+        <f>IF(J25&gt;0, VLOOKUP(J25-J$5-(INT($M25/9)+(MOD($M25,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="70">
+        <f>IF(K25&gt;0, VLOOKUP(K25-K$5-(INT($M25/9)+(MOD($M25,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="71">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="18">
+        <f>IF(L26&lt;&gt;"", L26, "")</f>
+        <v>6</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+    </row>
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="68">
+        <v>8</v>
+      </c>
+      <c r="D27" s="68">
+        <v>6</v>
+      </c>
+      <c r="E27" s="68">
+        <v>5</v>
+      </c>
+      <c r="F27" s="68">
+        <v>6</v>
+      </c>
+      <c r="G27" s="68">
+        <v>6</v>
+      </c>
+      <c r="H27" s="68">
+        <v>5</v>
+      </c>
+      <c r="I27" s="68">
+        <v>4</v>
+      </c>
+      <c r="J27" s="68">
+        <v>6</v>
+      </c>
+      <c r="K27" s="68">
+        <v>6</v>
+      </c>
+      <c r="L27" s="69">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="M27" s="12">
+        <v>11</v>
+      </c>
+      <c r="N27" s="12">
+        <f>IF(L27&lt;&gt;"",L27- M27, "")</f>
+        <v>41</v>
+      </c>
+      <c r="O27" s="14"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+    </row>
+    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="70">
+        <f>IF(C27&gt;0, VLOOKUP(C27-C$5-(INT($M27/9)+(MOD($M27,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="70">
+        <f>IF(D27&gt;0, VLOOKUP(D27-D$5-(INT($M27/9)+(MOD($M27,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="E28" s="70">
+        <f>IF(E27&gt;0, VLOOKUP(E27-E$5-(INT($M27/9)+(MOD($M27,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="F28" s="70">
+        <f>IF(F27&gt;0, VLOOKUP(F27-F$5-(INT($M27/9)+(MOD($M27,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="70">
+        <f>IF(G27&gt;0, VLOOKUP(G27-G$5-(INT($M27/9)+(MOD($M27,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="H28" s="70">
+        <f>IF(H27&gt;0, VLOOKUP(H27-H$5-(INT($M27/9)+(MOD($M27,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="I28" s="70">
+        <f>IF(I27&gt;0, VLOOKUP(I27-I$5-(INT($M27/9)+(MOD($M27,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="J28" s="70">
+        <f>IF(J27&gt;0, VLOOKUP(J27-J$5-(INT($M27/9)+(MOD($M27,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="K28" s="70">
+        <f>IF(K27&gt;0, VLOOKUP(K27-K$5-(INT($M27/9)+(MOD($M27,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="L28" s="71">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="18">
+        <f>IF(L28&lt;&gt;"", L28, "")</f>
+        <v>14</v>
+      </c>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+    </row>
+    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="68">
+        <v>5</v>
+      </c>
+      <c r="D29" s="68">
+        <v>6</v>
+      </c>
+      <c r="E29" s="68">
+        <v>5</v>
+      </c>
+      <c r="F29" s="68">
+        <v>5</v>
+      </c>
+      <c r="G29" s="68">
+        <v>5</v>
+      </c>
+      <c r="H29" s="68">
+        <v>5</v>
+      </c>
+      <c r="I29" s="68">
+        <v>5</v>
+      </c>
+      <c r="J29" s="68">
+        <v>7</v>
+      </c>
+      <c r="K29" s="68">
+        <v>7</v>
+      </c>
+      <c r="L29" s="69">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="M29" s="12">
+        <v>14</v>
+      </c>
+      <c r="N29" s="12">
+        <f>IF(L29&lt;&gt;"",L29- M29, "")</f>
+        <v>36</v>
+      </c>
+      <c r="O29" s="14"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+    </row>
+    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="70">
+        <f>IF(C29&gt;0, VLOOKUP(C29-C$5-(INT($M29/9)+(MOD($M29,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="D30" s="70">
+        <f>IF(D29&gt;0, VLOOKUP(D29-D$5-(INT($M29/9)+(MOD($M29,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="E30" s="70">
+        <f>IF(E29&gt;0, VLOOKUP(E29-E$5-(INT($M29/9)+(MOD($M29,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="F30" s="70">
+        <f>IF(F29&gt;0, VLOOKUP(F29-F$5-(INT($M29/9)+(MOD($M29,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="G30" s="70">
+        <f>IF(G29&gt;0, VLOOKUP(G29-G$5-(INT($M29/9)+(MOD($M29,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="H30" s="70">
+        <f>IF(H29&gt;0, VLOOKUP(H29-H$5-(INT($M29/9)+(MOD($M29,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="I30" s="70">
+        <f>IF(I29&gt;0, VLOOKUP(I29-I$5-(INT($M29/9)+(MOD($M29,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>1</v>
+      </c>
+      <c r="J30" s="70">
+        <f>IF(J29&gt;0, VLOOKUP(J29-J$5-(INT($M29/9)+(MOD($M29,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="70">
+        <f>IF(K29&gt;0, VLOOKUP(K29-K$5-(INT($M29/9)+(MOD($M29,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="L30" s="71">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="18">
+        <f>IF(L30&lt;&gt;"", L30, "")</f>
+        <v>18</v>
+      </c>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+    </row>
+    <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12">
+        <v>5</v>
+      </c>
+      <c r="D31" s="12">
+        <v>5</v>
+      </c>
+      <c r="E31" s="12">
+        <v>5</v>
+      </c>
+      <c r="F31" s="12">
+        <v>3</v>
+      </c>
+      <c r="G31" s="12">
+        <v>4</v>
+      </c>
+      <c r="H31" s="12">
+        <v>4</v>
+      </c>
+      <c r="I31" s="12">
+        <v>4</v>
+      </c>
+      <c r="J31" s="12">
+        <v>5</v>
+      </c>
+      <c r="K31" s="12">
+        <v>5</v>
+      </c>
+      <c r="L31" s="13">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="M31" s="12">
+        <v>8</v>
+      </c>
+      <c r="N31" s="12">
+        <f>IF(L31&lt;&gt;"",L31- M31, "")</f>
+        <v>32</v>
+      </c>
+      <c r="O31" s="14"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+    </row>
+    <row r="32" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16">
+        <f>IF(C31&gt;0, VLOOKUP(C31-C$5-(INT($M31/9)+(MOD($M31,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="D32" s="16">
+        <f>IF(D31&gt;0, VLOOKUP(D31-D$5-(INT($M31/9)+(MOD($M31,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="E32" s="16">
+        <f>IF(E31&gt;0, VLOOKUP(E31-E$5-(INT($M31/9)+(MOD($M31,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="F32" s="16">
+        <f>IF(F31&gt;0, VLOOKUP(F31-F$5-(INT($M31/9)+(MOD($M31,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G32" s="16">
+        <f>IF(G31&gt;0, VLOOKUP(G31-G$5-(INT($M31/9)+(MOD($M31,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="H32" s="16">
+        <f>IF(H31&gt;0, VLOOKUP(H31-H$5-(INT($M31/9)+(MOD($M31,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="I32" s="16">
+        <f>IF(I31&gt;0, VLOOKUP(I31-I$5-(INT($M31/9)+(MOD($M31,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="J32" s="16">
+        <f>IF(J31&gt;0, VLOOKUP(J31-J$5-(INT($M31/9)+(MOD($M31,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>2</v>
+      </c>
+      <c r="K32" s="16">
+        <f>IF(K31&gt;0, VLOOKUP(K31-K$5-(INT($M31/9)+(MOD($M31,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
+        <v>3</v>
+      </c>
+      <c r="L32" s="17">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="18">
+        <f>IF(L32&lt;&gt;"", L32, "")</f>
+        <v>22</v>
+      </c>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{02748716-3865-244E-B5BA-B837FD6542E8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="portrait"/>
+  <ignoredErrors>
+    <ignoredError sqref="L16 L12" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9351,23 +11166,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -9381,23 +11196,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -10301,23 +12116,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -10331,23 +12146,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -11983,23 +13798,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -12013,23 +13828,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -12933,23 +14748,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="17" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
+      <c r="A1" s="65" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
       <c r="P1" s="38"/>
       <c r="Q1" s="38"/>
       <c r="R1" s="38"/>
@@ -12963,23 +14778,23 @@
       <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="66" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
+      <c r="A2" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
       <c r="P2" s="38"/>
       <c r="Q2" s="38"/>
       <c r="R2" s="38"/>
@@ -13445,23 +15260,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -13475,23 +15290,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -14509,23 +16324,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -14539,23 +16354,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -16065,23 +17880,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -16095,23 +17910,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
+      <c r="A2" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>

--- a/public/results/2025/2025 Weekly Stats - Week 12.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD239960-DFDC-1344-A761-9FE852991918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB05767-DC91-474C-AA4B-A226B50DCCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="44200" yWindow="2000" windowWidth="26740" windowHeight="18000" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -416,7 +416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -598,18 +598,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8615,34 +8603,34 @@
         <v>34</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="68">
-        <v>6</v>
-      </c>
-      <c r="D9" s="68">
-        <v>5</v>
-      </c>
-      <c r="E9" s="68">
-        <v>5</v>
-      </c>
-      <c r="F9" s="68">
-        <v>4</v>
-      </c>
-      <c r="G9" s="68">
-        <v>6</v>
-      </c>
-      <c r="H9" s="68">
-        <v>4</v>
-      </c>
-      <c r="I9" s="68">
-        <v>3</v>
-      </c>
-      <c r="J9" s="68">
-        <v>5</v>
-      </c>
-      <c r="K9" s="68">
-        <v>6</v>
-      </c>
-      <c r="L9" s="69">
+      <c r="C9" s="12">
+        <v>6</v>
+      </c>
+      <c r="D9" s="12">
+        <v>5</v>
+      </c>
+      <c r="E9" s="12">
+        <v>5</v>
+      </c>
+      <c r="F9" s="12">
+        <v>4</v>
+      </c>
+      <c r="G9" s="12">
+        <v>6</v>
+      </c>
+      <c r="H9" s="12">
+        <v>4</v>
+      </c>
+      <c r="I9" s="12">
+        <v>3</v>
+      </c>
+      <c r="J9" s="12">
+        <v>5</v>
+      </c>
+      <c r="K9" s="12">
+        <v>6</v>
+      </c>
+      <c r="L9" s="13">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -8669,43 +8657,43 @@
     <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
-      <c r="C10" s="70">
+      <c r="C10" s="16">
         <f>IF(C9&gt;0, VLOOKUP(C9-C$5-(INT($M9/9)+(MOD($M9,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="D10" s="70">
+      <c r="D10" s="16">
         <f>IF(D9&gt;0, VLOOKUP(D9-D$5-(INT($M9/9)+(MOD($M9,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="16">
         <f>IF(E9&gt;0, VLOOKUP(E9-E$5-(INT($M9/9)+(MOD($M9,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="F10" s="70">
+      <c r="F10" s="16">
         <f>IF(F9&gt;0, VLOOKUP(F9-F$5-(INT($M9/9)+(MOD($M9,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="G10" s="70">
+      <c r="G10" s="16">
         <f>IF(G9&gt;0, VLOOKUP(G9-G$5-(INT($M9/9)+(MOD($M9,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="H10" s="70">
+      <c r="H10" s="16">
         <f>IF(H9&gt;0, VLOOKUP(H9-H$5-(INT($M9/9)+(MOD($M9,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="I10" s="70">
+      <c r="I10" s="16">
         <f>IF(I9&gt;0, VLOOKUP(I9-I$5-(INT($M9/9)+(MOD($M9,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="J10" s="70">
+      <c r="J10" s="16">
         <f>IF(J9&gt;0, VLOOKUP(J9-J$5-(INT($M9/9)+(MOD($M9,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="K10" s="70">
+      <c r="K10" s="16">
         <f>IF(K9&gt;0, VLOOKUP(K9-K$5-(INT($M9/9)+(MOD($M9,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="L10" s="71">
+      <c r="L10" s="17">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -8732,34 +8720,34 @@
         <v>33</v>
       </c>
       <c r="B11" s="12"/>
-      <c r="C11" s="68">
-        <v>5</v>
-      </c>
-      <c r="D11" s="68">
+      <c r="C11" s="12">
+        <v>5</v>
+      </c>
+      <c r="D11" s="12">
         <v>7</v>
       </c>
-      <c r="E11" s="68">
-        <v>5</v>
-      </c>
-      <c r="F11" s="68">
-        <v>4</v>
-      </c>
-      <c r="G11" s="68">
-        <v>6</v>
-      </c>
-      <c r="H11" s="68">
-        <v>5</v>
-      </c>
-      <c r="I11" s="68">
-        <v>3</v>
-      </c>
-      <c r="J11" s="68">
-        <v>5</v>
-      </c>
-      <c r="K11" s="68">
+      <c r="E11" s="12">
+        <v>5</v>
+      </c>
+      <c r="F11" s="12">
+        <v>4</v>
+      </c>
+      <c r="G11" s="12">
+        <v>6</v>
+      </c>
+      <c r="H11" s="12">
+        <v>5</v>
+      </c>
+      <c r="I11" s="12">
+        <v>3</v>
+      </c>
+      <c r="J11" s="12">
+        <v>5</v>
+      </c>
+      <c r="K11" s="12">
         <v>7</v>
       </c>
-      <c r="L11" s="69">
+      <c r="L11" s="13">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
@@ -8786,43 +8774,43 @@
     <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
-      <c r="C12" s="70">
+      <c r="C12" s="16">
         <f>IF(C11&gt;0, VLOOKUP(C11-C$5-(INT($M11/9)+(MOD($M11,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="D12" s="70">
+      <c r="D12" s="16">
         <f>IF(D11&gt;0, VLOOKUP(D11-D$5-(INT($M11/9)+(MOD($M11,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="16">
         <f>IF(E11&gt;0, VLOOKUP(E11-E$5-(INT($M11/9)+(MOD($M11,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="F12" s="70">
+      <c r="F12" s="16">
         <f>IF(F11&gt;0, VLOOKUP(F11-F$5-(INT($M11/9)+(MOD($M11,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="G12" s="70">
+      <c r="G12" s="16">
         <f>IF(G11&gt;0, VLOOKUP(G11-G$5-(INT($M11/9)+(MOD($M11,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="H12" s="70">
+      <c r="H12" s="16">
         <f>IF(H11&gt;0, VLOOKUP(H11-H$5-(INT($M11/9)+(MOD($M11,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="I12" s="70">
+      <c r="I12" s="16">
         <f>IF(I11&gt;0, VLOOKUP(I11-I$5-(INT($M11/9)+(MOD($M11,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="J12" s="70">
+      <c r="J12" s="16">
         <f>IF(J11&gt;0, VLOOKUP(J11-J$5-(INT($M11/9)+(MOD($M11,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="K12" s="70">
+      <c r="K12" s="16">
         <f>IF(K11&gt;0, VLOOKUP(K11-K$5-(INT($M11/9)+(MOD($M11,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="L12" s="71">
+      <c r="L12" s="17">
         <f t="shared" ref="L12" si="1">IF(SUM(C12:K12)&gt;0, SUM(C12:K12),"")</f>
         <v>16</v>
       </c>
@@ -8849,34 +8837,34 @@
         <v>29</v>
       </c>
       <c r="B13" s="12"/>
-      <c r="C13" s="68">
-        <v>5</v>
-      </c>
-      <c r="D13" s="68">
+      <c r="C13" s="12">
+        <v>5</v>
+      </c>
+      <c r="D13" s="12">
         <v>7</v>
       </c>
-      <c r="E13" s="68">
-        <v>5</v>
-      </c>
-      <c r="F13" s="68">
-        <v>5</v>
-      </c>
-      <c r="G13" s="68">
-        <v>6</v>
-      </c>
-      <c r="H13" s="68">
-        <v>5</v>
-      </c>
-      <c r="I13" s="68">
-        <v>4</v>
-      </c>
-      <c r="J13" s="68">
-        <v>6</v>
-      </c>
-      <c r="K13" s="68">
+      <c r="E13" s="12">
+        <v>5</v>
+      </c>
+      <c r="F13" s="12">
+        <v>5</v>
+      </c>
+      <c r="G13" s="12">
+        <v>6</v>
+      </c>
+      <c r="H13" s="12">
+        <v>5</v>
+      </c>
+      <c r="I13" s="12">
+        <v>4</v>
+      </c>
+      <c r="J13" s="12">
+        <v>6</v>
+      </c>
+      <c r="K13" s="12">
         <v>7</v>
       </c>
-      <c r="L13" s="69">
+      <c r="L13" s="13">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -8903,43 +8891,43 @@
     <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
-      <c r="C14" s="70">
+      <c r="C14" s="16">
         <f>IF(C13&gt;0, VLOOKUP(C13-C$5-(INT($M13/9)+(MOD($M13,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="D14" s="70">
+      <c r="D14" s="16">
         <f>IF(D13&gt;0, VLOOKUP(D13-D$5-(INT($M13/9)+(MOD($M13,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="16">
         <f>IF(E13&gt;0, VLOOKUP(E13-E$5-(INT($M13/9)+(MOD($M13,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="F14" s="70">
+      <c r="F14" s="16">
         <f>IF(F13&gt;0, VLOOKUP(F13-F$5-(INT($M13/9)+(MOD($M13,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="G14" s="70">
+      <c r="G14" s="16">
         <f>IF(G13&gt;0, VLOOKUP(G13-G$5-(INT($M13/9)+(MOD($M13,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="H14" s="70">
+      <c r="H14" s="16">
         <f>IF(H13&gt;0, VLOOKUP(H13-H$5-(INT($M13/9)+(MOD($M13,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="I14" s="70">
+      <c r="I14" s="16">
         <f>IF(I13&gt;0, VLOOKUP(I13-I$5-(INT($M13/9)+(MOD($M13,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="J14" s="70">
+      <c r="J14" s="16">
         <f>IF(J13&gt;0, VLOOKUP(J13-J$5-(INT($M13/9)+(MOD($M13,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="K14" s="70">
+      <c r="K14" s="16">
         <f>IF(K13&gt;0, VLOOKUP(K13-K$5-(INT($M13/9)+(MOD($M13,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="L14" s="71">
+      <c r="L14" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -8966,34 +8954,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="68">
-        <v>5</v>
-      </c>
-      <c r="D15" s="68">
+      <c r="C15" s="12">
+        <v>5</v>
+      </c>
+      <c r="D15" s="12">
         <v>7</v>
       </c>
-      <c r="E15" s="68">
-        <v>5</v>
-      </c>
-      <c r="F15" s="68">
-        <v>5</v>
-      </c>
-      <c r="G15" s="68">
-        <v>6</v>
-      </c>
-      <c r="H15" s="68">
+      <c r="E15" s="12">
+        <v>5</v>
+      </c>
+      <c r="F15" s="12">
+        <v>5</v>
+      </c>
+      <c r="G15" s="12">
+        <v>6</v>
+      </c>
+      <c r="H15" s="12">
         <v>7</v>
       </c>
-      <c r="I15" s="68">
-        <v>5</v>
-      </c>
-      <c r="J15" s="68">
-        <v>5</v>
-      </c>
-      <c r="K15" s="68">
+      <c r="I15" s="12">
+        <v>5</v>
+      </c>
+      <c r="J15" s="12">
+        <v>5</v>
+      </c>
+      <c r="K15" s="12">
         <v>7</v>
       </c>
-      <c r="L15" s="69">
+      <c r="L15" s="13">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
@@ -9020,43 +9008,43 @@
     <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
-      <c r="C16" s="70">
+      <c r="C16" s="16">
         <f>IF(C15&gt;0, VLOOKUP(C15-C$5-(INT($M15/9)+(MOD($M15,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="D16" s="70">
+      <c r="D16" s="16">
         <f>IF(D15&gt;0, VLOOKUP(D15-D$5-(INT($M15/9)+(MOD($M15,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="E16" s="70">
+      <c r="E16" s="16">
         <f>IF(E15&gt;0, VLOOKUP(E15-E$5-(INT($M15/9)+(MOD($M15,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="F16" s="70">
+      <c r="F16" s="16">
         <f>IF(F15&gt;0, VLOOKUP(F15-F$5-(INT($M15/9)+(MOD($M15,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="G16" s="70">
+      <c r="G16" s="16">
         <f>IF(G15&gt;0, VLOOKUP(G15-G$5-(INT($M15/9)+(MOD($M15,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="H16" s="70">
+      <c r="H16" s="16">
         <f>IF(H15&gt;0, VLOOKUP(H15-H$5-(INT($M15/9)+(MOD($M15,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="70">
+      <c r="I16" s="16">
         <f>IF(I15&gt;0, VLOOKUP(I15-I$5-(INT($M15/9)+(MOD($M15,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="J16" s="70">
+      <c r="J16" s="16">
         <f>IF(J15&gt;0, VLOOKUP(J15-J$5-(INT($M15/9)+(MOD($M15,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="K16" s="70">
+      <c r="K16" s="16">
         <f>IF(K15&gt;0, VLOOKUP(K15-K$5-(INT($M15/9)+(MOD($M15,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="L16" s="71">
+      <c r="L16" s="17">
         <f t="shared" ref="L16" si="2">IF(SUM(C16:K16)&gt;0, SUM(C16:K16),"")</f>
         <v>13</v>
       </c>
@@ -9083,34 +9071,34 @@
         <v>15</v>
       </c>
       <c r="B17" s="12"/>
-      <c r="C17" s="68">
-        <v>5</v>
-      </c>
-      <c r="D17" s="68">
-        <v>6</v>
-      </c>
-      <c r="E17" s="68">
-        <v>5</v>
-      </c>
-      <c r="F17" s="68">
-        <v>6</v>
-      </c>
-      <c r="G17" s="68">
+      <c r="C17" s="12">
+        <v>5</v>
+      </c>
+      <c r="D17" s="12">
+        <v>6</v>
+      </c>
+      <c r="E17" s="12">
+        <v>5</v>
+      </c>
+      <c r="F17" s="12">
+        <v>6</v>
+      </c>
+      <c r="G17" s="12">
         <v>8</v>
       </c>
-      <c r="H17" s="68">
-        <v>5</v>
-      </c>
-      <c r="I17" s="68">
-        <v>6</v>
-      </c>
-      <c r="J17" s="68">
-        <v>6</v>
-      </c>
-      <c r="K17" s="68">
+      <c r="H17" s="12">
+        <v>5</v>
+      </c>
+      <c r="I17" s="12">
+        <v>6</v>
+      </c>
+      <c r="J17" s="12">
+        <v>6</v>
+      </c>
+      <c r="K17" s="12">
         <v>7</v>
       </c>
-      <c r="L17" s="69">
+      <c r="L17" s="13">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
@@ -9137,43 +9125,43 @@
     <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
-      <c r="C18" s="70">
+      <c r="C18" s="16">
         <f>IF(C17&gt;0, VLOOKUP(C17-C$5-(INT($M17/9)+(MOD($M17,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="D18" s="70">
+      <c r="D18" s="16">
         <f>IF(D17&gt;0, VLOOKUP(D17-D$5-(INT($M17/9)+(MOD($M17,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="E18" s="70">
+      <c r="E18" s="16">
         <f>IF(E17&gt;0, VLOOKUP(E17-E$5-(INT($M17/9)+(MOD($M17,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="F18" s="70">
+      <c r="F18" s="16">
         <f>IF(F17&gt;0, VLOOKUP(F17-F$5-(INT($M17/9)+(MOD($M17,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="G18" s="70">
+      <c r="G18" s="16">
         <f>IF(G17&gt;0, VLOOKUP(G17-G$5-(INT($M17/9)+(MOD($M17,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="H18" s="70">
+      <c r="H18" s="16">
         <f>IF(H17&gt;0, VLOOKUP(H17-H$5-(INT($M17/9)+(MOD($M17,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="I18" s="70">
+      <c r="I18" s="16">
         <f>IF(I17&gt;0, VLOOKUP(I17-I$5-(INT($M17/9)+(MOD($M17,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="J18" s="70">
+      <c r="J18" s="16">
         <f>IF(J17&gt;0, VLOOKUP(J17-J$5-(INT($M17/9)+(MOD($M17,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="K18" s="70">
+      <c r="K18" s="16">
         <f>IF(K17&gt;0, VLOOKUP(K17-K$5-(INT($M17/9)+(MOD($M17,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="L18" s="71">
+      <c r="L18" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -9200,34 +9188,34 @@
         <v>16</v>
       </c>
       <c r="B19" s="12"/>
-      <c r="C19" s="68">
+      <c r="C19" s="12">
         <v>8</v>
       </c>
-      <c r="D19" s="68">
-        <v>5</v>
-      </c>
-      <c r="E19" s="68">
-        <v>5</v>
-      </c>
-      <c r="F19" s="68">
-        <v>3</v>
-      </c>
-      <c r="G19" s="68">
-        <v>6</v>
-      </c>
-      <c r="H19" s="68">
-        <v>5</v>
-      </c>
-      <c r="I19" s="68">
-        <v>6</v>
-      </c>
-      <c r="J19" s="68">
-        <v>6</v>
-      </c>
-      <c r="K19" s="68">
-        <v>6</v>
-      </c>
-      <c r="L19" s="69">
+      <c r="D19" s="12">
+        <v>5</v>
+      </c>
+      <c r="E19" s="12">
+        <v>5</v>
+      </c>
+      <c r="F19" s="12">
+        <v>3</v>
+      </c>
+      <c r="G19" s="12">
+        <v>6</v>
+      </c>
+      <c r="H19" s="12">
+        <v>5</v>
+      </c>
+      <c r="I19" s="12">
+        <v>6</v>
+      </c>
+      <c r="J19" s="12">
+        <v>6</v>
+      </c>
+      <c r="K19" s="12">
+        <v>6</v>
+      </c>
+      <c r="L19" s="13">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -9254,43 +9242,43 @@
     <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
-      <c r="C20" s="70">
+      <c r="C20" s="16">
         <f>IF(C19&gt;0, VLOOKUP(C19-C$5-(INT($M19/9)+(MOD($M19,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="D20" s="70">
+      <c r="D20" s="16">
         <f>IF(D19&gt;0, VLOOKUP(D19-D$5-(INT($M19/9)+(MOD($M19,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>4</v>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="16">
         <f>IF(E19&gt;0, VLOOKUP(E19-E$5-(INT($M19/9)+(MOD($M19,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="F20" s="70">
+      <c r="F20" s="16">
         <f>IF(F19&gt;0, VLOOKUP(F19-F$5-(INT($M19/9)+(MOD($M19,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="G20" s="70">
+      <c r="G20" s="16">
         <f>IF(G19&gt;0, VLOOKUP(G19-G$5-(INT($M19/9)+(MOD($M19,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="H20" s="70">
+      <c r="H20" s="16">
         <f>IF(H19&gt;0, VLOOKUP(H19-H$5-(INT($M19/9)+(MOD($M19,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="I20" s="70">
+      <c r="I20" s="16">
         <f>IF(I19&gt;0, VLOOKUP(I19-I$5-(INT($M19/9)+(MOD($M19,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="J20" s="70">
+      <c r="J20" s="16">
         <f>IF(J19&gt;0, VLOOKUP(J19-J$5-(INT($M19/9)+(MOD($M19,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="K20" s="70">
+      <c r="K20" s="16">
         <f>IF(K19&gt;0, VLOOKUP(K19-K$5-(INT($M19/9)+(MOD($M19,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="L20" s="71">
+      <c r="L20" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -9317,34 +9305,34 @@
         <v>36</v>
       </c>
       <c r="B21" s="12"/>
-      <c r="C21" s="68">
-        <v>4</v>
-      </c>
-      <c r="D21" s="68">
-        <v>5</v>
-      </c>
-      <c r="E21" s="68">
-        <v>4</v>
-      </c>
-      <c r="F21" s="68">
-        <v>4</v>
-      </c>
-      <c r="G21" s="68">
-        <v>4</v>
-      </c>
-      <c r="H21" s="68">
-        <v>4</v>
-      </c>
-      <c r="I21" s="68">
-        <v>3</v>
-      </c>
-      <c r="J21" s="68">
-        <v>5</v>
-      </c>
-      <c r="K21" s="68">
-        <v>5</v>
-      </c>
-      <c r="L21" s="69">
+      <c r="C21" s="12">
+        <v>4</v>
+      </c>
+      <c r="D21" s="12">
+        <v>5</v>
+      </c>
+      <c r="E21" s="12">
+        <v>4</v>
+      </c>
+      <c r="F21" s="12">
+        <v>4</v>
+      </c>
+      <c r="G21" s="12">
+        <v>4</v>
+      </c>
+      <c r="H21" s="12">
+        <v>4</v>
+      </c>
+      <c r="I21" s="12">
+        <v>3</v>
+      </c>
+      <c r="J21" s="12">
+        <v>5</v>
+      </c>
+      <c r="K21" s="12">
+        <v>5</v>
+      </c>
+      <c r="L21" s="13">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -9371,43 +9359,43 @@
     <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
-      <c r="C22" s="70">
+      <c r="C22" s="16">
         <f>IF(C21&gt;0, VLOOKUP(C21-C$5-(INT($M21/9)+(MOD($M21,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="D22" s="70">
+      <c r="D22" s="16">
         <f>IF(D21&gt;0, VLOOKUP(D21-D$5-(INT($M21/9)+(MOD($M21,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="E22" s="70">
+      <c r="E22" s="16">
         <f>IF(E21&gt;0, VLOOKUP(E21-E$5-(INT($M21/9)+(MOD($M21,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="F22" s="70">
+      <c r="F22" s="16">
         <f>IF(F21&gt;0, VLOOKUP(F21-F$5-(INT($M21/9)+(MOD($M21,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="G22" s="70">
+      <c r="G22" s="16">
         <f>IF(G21&gt;0, VLOOKUP(G21-G$5-(INT($M21/9)+(MOD($M21,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="H22" s="70">
+      <c r="H22" s="16">
         <f>IF(H21&gt;0, VLOOKUP(H21-H$5-(INT($M21/9)+(MOD($M21,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="I22" s="70">
+      <c r="I22" s="16">
         <f>IF(I21&gt;0, VLOOKUP(I21-I$5-(INT($M21/9)+(MOD($M21,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="J22" s="70">
+      <c r="J22" s="16">
         <f>IF(J21&gt;0, VLOOKUP(J21-J$5-(INT($M21/9)+(MOD($M21,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="K22" s="70">
+      <c r="K22" s="16">
         <f>IF(K21&gt;0, VLOOKUP(K21-K$5-(INT($M21/9)+(MOD($M21,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="L22" s="71">
+      <c r="L22" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -9434,34 +9422,34 @@
         <v>11</v>
       </c>
       <c r="B23" s="12"/>
-      <c r="C23" s="68">
-        <v>5</v>
-      </c>
-      <c r="D23" s="68">
-        <v>5</v>
-      </c>
-      <c r="E23" s="68">
-        <v>5</v>
-      </c>
-      <c r="F23" s="68">
-        <v>4</v>
-      </c>
-      <c r="G23" s="68">
-        <v>4</v>
-      </c>
-      <c r="H23" s="68">
-        <v>4</v>
-      </c>
-      <c r="I23" s="68">
-        <v>4</v>
-      </c>
-      <c r="J23" s="68">
-        <v>4</v>
-      </c>
-      <c r="K23" s="68">
-        <v>6</v>
-      </c>
-      <c r="L23" s="69">
+      <c r="C23" s="12">
+        <v>5</v>
+      </c>
+      <c r="D23" s="12">
+        <v>5</v>
+      </c>
+      <c r="E23" s="12">
+        <v>5</v>
+      </c>
+      <c r="F23" s="12">
+        <v>4</v>
+      </c>
+      <c r="G23" s="12">
+        <v>4</v>
+      </c>
+      <c r="H23" s="12">
+        <v>4</v>
+      </c>
+      <c r="I23" s="12">
+        <v>4</v>
+      </c>
+      <c r="J23" s="12">
+        <v>4</v>
+      </c>
+      <c r="K23" s="12">
+        <v>6</v>
+      </c>
+      <c r="L23" s="13">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -9488,43 +9476,43 @@
     <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="70">
+      <c r="C24" s="16">
         <f>IF(C23&gt;0, VLOOKUP(C23-C$5-(INT($M23/9)+(MOD($M23,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="D24" s="70">
+      <c r="D24" s="16">
         <f>IF(D23&gt;0, VLOOKUP(D23-D$5-(INT($M23/9)+(MOD($M23,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="E24" s="70">
+      <c r="E24" s="16">
         <f>IF(E23&gt;0, VLOOKUP(E23-E$5-(INT($M23/9)+(MOD($M23,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="F24" s="70">
+      <c r="F24" s="16">
         <f>IF(F23&gt;0, VLOOKUP(F23-F$5-(INT($M23/9)+(MOD($M23,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="G24" s="70">
+      <c r="G24" s="16">
         <f>IF(G23&gt;0, VLOOKUP(G23-G$5-(INT($M23/9)+(MOD($M23,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="H24" s="70">
+      <c r="H24" s="16">
         <f>IF(H23&gt;0, VLOOKUP(H23-H$5-(INT($M23/9)+(MOD($M23,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="I24" s="70">
+      <c r="I24" s="16">
         <f>IF(I23&gt;0, VLOOKUP(I23-I$5-(INT($M23/9)+(MOD($M23,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="J24" s="70">
+      <c r="J24" s="16">
         <f>IF(J23&gt;0, VLOOKUP(J23-J$5-(INT($M23/9)+(MOD($M23,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="K24" s="70">
+      <c r="K24" s="16">
         <f>IF(K23&gt;0, VLOOKUP(K23-K$5-(INT($M23/9)+(MOD($M23,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="L24" s="71">
+      <c r="L24" s="17">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -9551,34 +9539,34 @@
         <v>28</v>
       </c>
       <c r="B25" s="12"/>
-      <c r="C25" s="68">
-        <v>6</v>
-      </c>
-      <c r="D25" s="68">
+      <c r="C25" s="12">
+        <v>6</v>
+      </c>
+      <c r="D25" s="12">
         <v>10</v>
       </c>
-      <c r="E25" s="68">
+      <c r="E25" s="12">
         <v>8</v>
       </c>
-      <c r="F25" s="68">
-        <v>6</v>
-      </c>
-      <c r="G25" s="68">
+      <c r="F25" s="12">
+        <v>6</v>
+      </c>
+      <c r="G25" s="12">
         <v>8</v>
       </c>
-      <c r="H25" s="68">
+      <c r="H25" s="12">
         <v>8</v>
       </c>
-      <c r="I25" s="68">
-        <v>6</v>
-      </c>
-      <c r="J25" s="68">
+      <c r="I25" s="12">
+        <v>6</v>
+      </c>
+      <c r="J25" s="12">
         <v>8</v>
       </c>
-      <c r="K25" s="68">
+      <c r="K25" s="12">
         <v>10</v>
       </c>
-      <c r="L25" s="69">
+      <c r="L25" s="13">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
@@ -9605,43 +9593,43 @@
     <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
-      <c r="C26" s="70">
+      <c r="C26" s="16">
         <f>IF(C25&gt;0, VLOOKUP(C25-C$5-(INT($M25/9)+(MOD($M25,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="D26" s="70">
+      <c r="D26" s="16">
         <f>IF(D25&gt;0, VLOOKUP(D25-D$5-(INT($M25/9)+(MOD($M25,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="E26" s="70">
+      <c r="E26" s="16">
         <f>IF(E25&gt;0, VLOOKUP(E25-E$5-(INT($M25/9)+(MOD($M25,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="F26" s="70">
+      <c r="F26" s="16">
         <f>IF(F25&gt;0, VLOOKUP(F25-F$5-(INT($M25/9)+(MOD($M25,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="G26" s="70">
+      <c r="G26" s="16">
         <f>IF(G25&gt;0, VLOOKUP(G25-G$5-(INT($M25/9)+(MOD($M25,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="H26" s="70">
+      <c r="H26" s="16">
         <f>IF(H25&gt;0, VLOOKUP(H25-H$5-(INT($M25/9)+(MOD($M25,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="I26" s="70">
+      <c r="I26" s="16">
         <f>IF(I25&gt;0, VLOOKUP(I25-I$5-(INT($M25/9)+(MOD($M25,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="J26" s="70">
+      <c r="J26" s="16">
         <f>IF(J25&gt;0, VLOOKUP(J25-J$5-(INT($M25/9)+(MOD($M25,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="K26" s="70">
+      <c r="K26" s="16">
         <f>IF(K25&gt;0, VLOOKUP(K25-K$5-(INT($M25/9)+(MOD($M25,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="L26" s="71">
+      <c r="L26" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -9668,34 +9656,34 @@
         <v>35</v>
       </c>
       <c r="B27" s="12"/>
-      <c r="C27" s="68">
+      <c r="C27" s="12">
         <v>8</v>
       </c>
-      <c r="D27" s="68">
-        <v>6</v>
-      </c>
-      <c r="E27" s="68">
-        <v>5</v>
-      </c>
-      <c r="F27" s="68">
-        <v>6</v>
-      </c>
-      <c r="G27" s="68">
-        <v>6</v>
-      </c>
-      <c r="H27" s="68">
-        <v>5</v>
-      </c>
-      <c r="I27" s="68">
-        <v>4</v>
-      </c>
-      <c r="J27" s="68">
-        <v>6</v>
-      </c>
-      <c r="K27" s="68">
-        <v>6</v>
-      </c>
-      <c r="L27" s="69">
+      <c r="D27" s="12">
+        <v>6</v>
+      </c>
+      <c r="E27" s="12">
+        <v>5</v>
+      </c>
+      <c r="F27" s="12">
+        <v>6</v>
+      </c>
+      <c r="G27" s="12">
+        <v>6</v>
+      </c>
+      <c r="H27" s="12">
+        <v>5</v>
+      </c>
+      <c r="I27" s="12">
+        <v>4</v>
+      </c>
+      <c r="J27" s="12">
+        <v>6</v>
+      </c>
+      <c r="K27" s="12">
+        <v>6</v>
+      </c>
+      <c r="L27" s="13">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
@@ -9722,43 +9710,43 @@
     <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
-      <c r="C28" s="70">
+      <c r="C28" s="16">
         <f>IF(C27&gt;0, VLOOKUP(C27-C$5-(INT($M27/9)+(MOD($M27,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="D28" s="70">
+      <c r="D28" s="16">
         <f>IF(D27&gt;0, VLOOKUP(D27-D$5-(INT($M27/9)+(MOD($M27,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="70">
+      <c r="E28" s="16">
         <f>IF(E27&gt;0, VLOOKUP(E27-E$5-(INT($M27/9)+(MOD($M27,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="F28" s="70">
+      <c r="F28" s="16">
         <f>IF(F27&gt;0, VLOOKUP(F27-F$5-(INT($M27/9)+(MOD($M27,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="G28" s="70">
+      <c r="G28" s="16">
         <f>IF(G27&gt;0, VLOOKUP(G27-G$5-(INT($M27/9)+(MOD($M27,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="H28" s="70">
+      <c r="H28" s="16">
         <f>IF(H27&gt;0, VLOOKUP(H27-H$5-(INT($M27/9)+(MOD($M27,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="I28" s="70">
+      <c r="I28" s="16">
         <f>IF(I27&gt;0, VLOOKUP(I27-I$5-(INT($M27/9)+(MOD($M27,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="J28" s="70">
+      <c r="J28" s="16">
         <f>IF(J27&gt;0, VLOOKUP(J27-J$5-(INT($M27/9)+(MOD($M27,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="K28" s="70">
+      <c r="K28" s="16">
         <f>IF(K27&gt;0, VLOOKUP(K27-K$5-(INT($M27/9)+(MOD($M27,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="L28" s="71">
+      <c r="L28" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -9785,34 +9773,34 @@
         <v>37</v>
       </c>
       <c r="B29" s="12"/>
-      <c r="C29" s="68">
-        <v>5</v>
-      </c>
-      <c r="D29" s="68">
-        <v>6</v>
-      </c>
-      <c r="E29" s="68">
-        <v>5</v>
-      </c>
-      <c r="F29" s="68">
-        <v>5</v>
-      </c>
-      <c r="G29" s="68">
-        <v>5</v>
-      </c>
-      <c r="H29" s="68">
-        <v>5</v>
-      </c>
-      <c r="I29" s="68">
-        <v>5</v>
-      </c>
-      <c r="J29" s="68">
+      <c r="C29" s="12">
+        <v>5</v>
+      </c>
+      <c r="D29" s="12">
+        <v>6</v>
+      </c>
+      <c r="E29" s="12">
+        <v>5</v>
+      </c>
+      <c r="F29" s="12">
+        <v>5</v>
+      </c>
+      <c r="G29" s="12">
+        <v>5</v>
+      </c>
+      <c r="H29" s="12">
+        <v>5</v>
+      </c>
+      <c r="I29" s="12">
+        <v>5</v>
+      </c>
+      <c r="J29" s="12">
         <v>7</v>
       </c>
-      <c r="K29" s="68">
+      <c r="K29" s="12">
         <v>7</v>
       </c>
-      <c r="L29" s="69">
+      <c r="L29" s="13">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -9839,43 +9827,43 @@
     <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
-      <c r="C30" s="70">
+      <c r="C30" s="16">
         <f>IF(C29&gt;0, VLOOKUP(C29-C$5-(INT($M29/9)+(MOD($M29,9)&gt;=C$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="D30" s="70">
+      <c r="D30" s="16">
         <f>IF(D29&gt;0, VLOOKUP(D29-D$5-(INT($M29/9)+(MOD($M29,9)&gt;=D$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="E30" s="70">
+      <c r="E30" s="16">
         <f>IF(E29&gt;0, VLOOKUP(E29-E$5-(INT($M29/9)+(MOD($M29,9)&gt;=E$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="F30" s="70">
+      <c r="F30" s="16">
         <f>IF(F29&gt;0, VLOOKUP(F29-F$5-(INT($M29/9)+(MOD($M29,9)&gt;=F$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="G30" s="70">
+      <c r="G30" s="16">
         <f>IF(G29&gt;0, VLOOKUP(G29-G$5-(INT($M29/9)+(MOD($M29,9)&gt;=G$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
-      <c r="H30" s="70">
+      <c r="H30" s="16">
         <f>IF(H29&gt;0, VLOOKUP(H29-H$5-(INT($M29/9)+(MOD($M29,9)&gt;=H$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="I30" s="70">
+      <c r="I30" s="16">
         <f>IF(I29&gt;0, VLOOKUP(I29-I$5-(INT($M29/9)+(MOD($M29,9)&gt;=I$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="J30" s="70">
+      <c r="J30" s="16">
         <f>IF(J29&gt;0, VLOOKUP(J29-J$5-(INT($M29/9)+(MOD($M29,9)&gt;=J$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>0</v>
       </c>
-      <c r="K30" s="70">
+      <c r="K30" s="16">
         <f>IF(K29&gt;0, VLOOKUP(K29-K$5-(INT($M29/9)+(MOD($M29,9)&gt;=K$6)), '[2]Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="L30" s="71">
+      <c r="L30" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
